--- a/templates/SolidPro_CC_Master_Template.xlsx
+++ b/templates/SolidPro_CC_Master_Template.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
   <si>
     <t>CC_Code</t>
   </si>
@@ -124,6 +124,60 @@
     <t>Close_Date</t>
   </si>
   <si>
+    <t>SolidPro Cost Centre Portal — Cost Centre Master template</t>
+  </si>
+  <si>
+    <t>Enter your rows on the "CC_Master" sheet under the header row. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Unique code: &lt;Entity&gt;-&lt;BU code&gt;-&lt;number&gt;, e.g. IN-ENG-101. Prefix must equal Entity.</t>
+  </si>
+  <si>
+    <t>Unique friendly name (2-80 chars), e.g. Design Chennai</t>
+  </si>
+  <si>
+    <t>IN, US or UK</t>
+  </si>
+  <si>
+    <t>Business unit, e.g. Engineering / Shared Services / Sales</t>
+  </si>
+  <si>
+    <t>Department name</t>
+  </si>
+  <si>
+    <t>Direct, Shared or Allocated</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Search words separated by ; (e.g. cad; solidworks; chennai)</t>
+  </si>
+  <si>
+    <t>Active or Inactive (Inactive needs Close_Date). Never delete rows — deactivate.</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD or DD/MM/YYYY</t>
+  </si>
+  <si>
+    <t>Required when Status = Inactive; must be on/after Start_Date</t>
+  </si>
+  <si>
+    <t>Example rows (for illustration only — do not copy blindly)</t>
+  </si>
+  <si>
     <t>IN-ENG-104</t>
   </si>
   <si>
@@ -173,64 +227,13 @@
   </si>
   <si>
     <t>2026-11-01</t>
-  </si>
-  <si>
-    <t>SolidPro Cost Centre Portal — Cost Centre Master template</t>
-  </si>
-  <si>
-    <t>Replace the example rows on the first sheet. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>Rule</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Unique code: &lt;Entity&gt;-&lt;BU code&gt;-&lt;number&gt;, e.g. IN-ENG-101. Prefix must equal Entity.</t>
-  </si>
-  <si>
-    <t>Unique friendly name (2-80 chars), e.g. Design Chennai</t>
-  </si>
-  <si>
-    <t>IN, US or UK</t>
-  </si>
-  <si>
-    <t>Business unit, e.g. Engineering / Shared Services / Sales</t>
-  </si>
-  <si>
-    <t>Department name</t>
-  </si>
-  <si>
-    <t>Direct, Shared or Allocated</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Search words separated by ; (e.g. cad; solidworks; chennai)</t>
-  </si>
-  <si>
-    <t>Active or Inactive (Inactive needs Close_Date). Never delete rows — deactivate.</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD or DD/MM/YYYY</t>
-  </si>
-  <si>
-    <t>Required when Status = Inactive; must be on/after Start_Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -250,6 +253,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16469D"/>
     </font>
   </fonts>
   <fills count="3">
@@ -277,13 +284,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="16" style="1" customWidth="1"/>
@@ -659,70 +667,6 @@
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -744,23 +688,23 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -768,10 +712,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -779,10 +723,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -790,10 +734,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -801,10 +745,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -812,10 +756,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -823,10 +767,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -834,10 +778,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -845,10 +789,10 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -856,10 +800,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -867,10 +811,111 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" t="s">
         <v>43</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
